--- a/artfynd/A 725-2026 artfynd.xlsx
+++ b/artfynd/A 725-2026 artfynd.xlsx
@@ -1243,53 +1243,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132896203</v>
+        <v>132885116</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nygrävningen, Dlr</t>
+          <t>Lillsveden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506729</v>
+        <v>506610</v>
       </c>
       <c r="R7" t="n">
-        <v>6675566</v>
+        <v>6674999</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,9 +1311,19 @@
           <t>2026-04-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,48 +1350,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132885116</v>
+        <v>132896203</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillsveden, Dlr</t>
+          <t>Nygrävningen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506610</v>
+        <v>506729</v>
       </c>
       <c r="R8" t="n">
-        <v>6674999</v>
+        <v>6675566</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,19 +1423,9 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 725-2026 artfynd.xlsx
+++ b/artfynd/A 725-2026 artfynd.xlsx
@@ -1243,48 +1243,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132885116</v>
+        <v>132896203</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lillsveden, Dlr</t>
+          <t>Nygrävningen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506610</v>
+        <v>506729</v>
       </c>
       <c r="R7" t="n">
-        <v>6674999</v>
+        <v>6675566</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,19 +1316,9 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,53 +1345,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132896203</v>
+        <v>132885116</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nygrävningen, Dlr</t>
+          <t>Lillsveden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506729</v>
+        <v>506610</v>
       </c>
       <c r="R8" t="n">
-        <v>6675566</v>
+        <v>6674999</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1423,9 +1413,19 @@
           <t>2026-04-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,53 +1452,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132896237</v>
+        <v>132895884</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nygrävningen, Dlr</t>
+          <t>Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506719</v>
+        <v>506443</v>
       </c>
       <c r="R9" t="n">
-        <v>6675527</v>
+        <v>6675485</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,48 +1549,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132895884</v>
+        <v>132896237</v>
       </c>
       <c r="B10" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hagmossen, Dlr</t>
+          <t>Nygrävningen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506443</v>
+        <v>506719</v>
       </c>
       <c r="R10" t="n">
-        <v>6675485</v>
+        <v>6675527</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 725-2026 artfynd.xlsx
+++ b/artfynd/A 725-2026 artfynd.xlsx
@@ -1452,48 +1452,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132895884</v>
+        <v>132896237</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hagmossen, Dlr</t>
+          <t>Nygrävningen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506443</v>
+        <v>506719</v>
       </c>
       <c r="R9" t="n">
-        <v>6675485</v>
+        <v>6675527</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,53 +1554,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132896237</v>
+        <v>132895884</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>99130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nygrävningen, Dlr</t>
+          <t>Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506719</v>
+        <v>506443</v>
       </c>
       <c r="R10" t="n">
-        <v>6675527</v>
+        <v>6675485</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 725-2026 artfynd.xlsx
+++ b/artfynd/A 725-2026 artfynd.xlsx
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132884240</v>
+        <v>132885366</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1038,21 +1038,26 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillsveden, Dlr</t>
+          <t>Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506555</v>
+        <v>506651</v>
       </c>
       <c r="R5" t="n">
-        <v>6674957</v>
+        <v>6675099</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1084,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1099,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Svarar när jag lockar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132885366</v>
+        <v>132884240</v>
       </c>
       <c r="B6" t="n">
-        <v>57136</v>
+        <v>57955</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,16 +1142,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1150,26 +1160,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hagmossen, Dlr</t>
+          <t>Lillsveden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506651</v>
+        <v>506555</v>
       </c>
       <c r="R6" t="n">
-        <v>6675099</v>
+        <v>6674957</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1201,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:16</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Svarar när jag lockar</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 725-2026 artfynd.xlsx
+++ b/artfynd/A 725-2026 artfynd.xlsx
@@ -1348,7 +1348,7 @@
         <v>132885116</v>
       </c>
       <c r="B8" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,48 +1452,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132895884</v>
+        <v>132896237</v>
       </c>
       <c r="B9" t="n">
-        <v>99130</v>
+        <v>57958</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hagmossen, Dlr</t>
+          <t>Nygrävningen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506443</v>
+        <v>506719</v>
       </c>
       <c r="R9" t="n">
-        <v>6675485</v>
+        <v>6675527</v>
       </c>
       <c r="S9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,53 +1554,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132896237</v>
+        <v>132895884</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>99132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Nygrävningen, Dlr</t>
+          <t>Hagmossen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>506719</v>
+        <v>506443</v>
       </c>
       <c r="R10" t="n">
-        <v>6675527</v>
+        <v>6675485</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>132886339</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>132885589</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>132899864</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>132899900</v>
       </c>
       <c r="B21" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>133008633</v>
       </c>
       <c r="B22" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>133009507</v>
       </c>
       <c r="B24" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>133235549</v>
       </c>
       <c r="B26" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>133235573</v>
       </c>
       <c r="B27" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>133235824</v>
       </c>
       <c r="B28" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133235614</v>
       </c>
       <c r="B29" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>133235562</v>
       </c>
       <c r="B30" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>133235748</v>
       </c>
       <c r="B31" t="n">
-        <v>92531</v>
+        <v>92533</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>133235600</v>
       </c>
       <c r="B32" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>133235631</v>
       </c>
       <c r="B33" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>133235654</v>
       </c>
       <c r="B34" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 725-2026 artfynd.xlsx
+++ b/artfynd/A 725-2026 artfynd.xlsx
@@ -1243,53 +1243,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132896203</v>
+        <v>132885116</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>99132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Nygrävningen, Dlr</t>
+          <t>Lillsveden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506729</v>
+        <v>506610</v>
       </c>
       <c r="R7" t="n">
-        <v>6675566</v>
+        <v>6674999</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,9 +1311,19 @@
           <t>2026-04-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,48 +1350,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132885116</v>
+        <v>132896203</v>
       </c>
       <c r="B8" t="n">
-        <v>99132</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillsveden, Dlr</t>
+          <t>Nygrävningen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506610</v>
+        <v>506729</v>
       </c>
       <c r="R8" t="n">
-        <v>6674999</v>
+        <v>6675566</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1413,19 +1423,9 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 725-2026 artfynd.xlsx
+++ b/artfynd/A 725-2026 artfynd.xlsx
@@ -2398,7 +2398,7 @@
         <v>132899864</v>
       </c>
       <c r="B18" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>132899900</v>
       </c>
       <c r="B21" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>133008633</v>
       </c>
       <c r="B22" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>133009507</v>
       </c>
       <c r="B24" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>133235549</v>
       </c>
       <c r="B26" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>133235573</v>
       </c>
       <c r="B27" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>133235824</v>
       </c>
       <c r="B28" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133235614</v>
       </c>
       <c r="B29" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>133235562</v>
       </c>
       <c r="B30" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>133235748</v>
       </c>
       <c r="B31" t="n">
-        <v>92533</v>
+        <v>92541</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>133235600</v>
       </c>
       <c r="B32" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>133235631</v>
       </c>
       <c r="B33" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>133235654</v>
       </c>
       <c r="B34" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 725-2026 artfynd.xlsx
+++ b/artfynd/A 725-2026 artfynd.xlsx
@@ -3249,7 +3249,7 @@
         <v>133235549</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>133235573</v>
       </c>
       <c r="B27" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>133235824</v>
       </c>
       <c r="B28" t="n">
-        <v>98005</v>
+        <v>98033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>133235614</v>
       </c>
       <c r="B29" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>133235562</v>
       </c>
       <c r="B30" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>133235748</v>
       </c>
       <c r="B31" t="n">
-        <v>92541</v>
+        <v>92532</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>133235600</v>
       </c>
       <c r="B32" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>133235631</v>
       </c>
       <c r="B33" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>133235654</v>
       </c>
       <c r="B34" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 725-2026 artfynd.xlsx
+++ b/artfynd/A 725-2026 artfynd.xlsx
@@ -3606,7 +3606,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133235614</v>
+        <v>133235562</v>
       </c>
       <c r="B29" t="n">
         <v>99168</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506459</v>
+        <v>506483</v>
       </c>
       <c r="R29" t="n">
-        <v>6675378</v>
+        <v>6675460</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133235562</v>
+        <v>133235614</v>
       </c>
       <c r="B30" t="n">
         <v>99168</v>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506483</v>
+        <v>506459</v>
       </c>
       <c r="R30" t="n">
-        <v>6675460</v>
+        <v>6675378</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>

--- a/artfynd/A 725-2026 artfynd.xlsx
+++ b/artfynd/A 725-2026 artfynd.xlsx
@@ -3249,7 +3249,7 @@
         <v>133235549</v>
       </c>
       <c r="B26" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>133235573</v>
       </c>
       <c r="B27" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>133235824</v>
       </c>
       <c r="B28" t="n">
-        <v>98033</v>
+        <v>98043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133235562</v>
+        <v>133235614</v>
       </c>
       <c r="B29" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>506483</v>
+        <v>506459</v>
       </c>
       <c r="R29" t="n">
-        <v>6675460</v>
+        <v>6675378</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133235614</v>
+        <v>133235562</v>
       </c>
       <c r="B30" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>506459</v>
+        <v>506483</v>
       </c>
       <c r="R30" t="n">
-        <v>6675378</v>
+        <v>6675460</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3849,7 +3849,7 @@
         <v>133235748</v>
       </c>
       <c r="B31" t="n">
-        <v>92532</v>
+        <v>92542</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>133235600</v>
       </c>
       <c r="B32" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>133235631</v>
       </c>
       <c r="B33" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>133235654</v>
       </c>
       <c r="B34" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
